--- a/Data/FlightPlan/FPL_17AUG26.xlsx
+++ b/Data/FlightPlan/FPL_17AUG26.xlsx
@@ -266,6 +266,9 @@
     <t>09:20</t>
   </si>
   <si>
+    <t>13:12</t>
+  </si>
+  <si>
     <t>TPE</t>
   </si>
   <si>
@@ -332,9 +335,6 @@
     <t>12:55</t>
   </si>
   <si>
-    <t>13:12</t>
-  </si>
-  <si>
     <t>UIH</t>
   </si>
   <si>
@@ -506,9 +506,6 @@
     <t>08:50</t>
   </si>
   <si>
-    <t>08:26</t>
-  </si>
-  <si>
     <t>11:55</t>
   </si>
   <si>
@@ -551,6 +548,9 @@
     <t>07:30</t>
   </si>
   <si>
+    <t>09:03</t>
+  </si>
+  <si>
     <t>HUI</t>
   </si>
   <si>
@@ -707,6 +707,9 @@
     <t>13:05</t>
   </si>
   <si>
+    <t>14:01</t>
+  </si>
+  <si>
     <t>16:05</t>
   </si>
   <si>
@@ -1313,7 +1316,7 @@
     <t>Total Record(s): 389</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 17, 2026 07:32</t>
+    <t xml:space="preserve">Generated on  Aug 17, 2026 07:46</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2774,7 +2777,9 @@
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
+      <c t="s" r="M36" s="7">
+        <v>85</v>
+      </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c t="s" r="A37" s="6">
@@ -2797,13 +2802,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2827,13 +2832,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G38" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H38" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J38" s="7">
         <v>68</v>
@@ -2863,13 +2868,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H39" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2902,7 +2907,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -2914,10 +2919,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2935,7 +2940,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -2947,10 +2952,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2968,7 +2973,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -2980,10 +2985,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -3001,7 +3006,7 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -3010,13 +3015,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -3034,22 +3039,22 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="H45" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3082,27 +3087,27 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3117,7 +3122,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3150,7 +3155,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3165,7 +3170,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3183,7 +3188,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3216,7 +3221,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3249,7 +3254,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3490,7 +3495,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="I60" s="7">
         <v>39</v>
@@ -3520,7 +3525,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>28</v>
@@ -3556,13 +3561,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="I62" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3715,7 +3720,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3978,7 +3983,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -4157,7 +4162,7 @@
         <v>159</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J82" s="7">
         <v>80</v>
@@ -4246,7 +4251,7 @@
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>165</v>
+        <v>51</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4276,7 +4281,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4306,7 +4311,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>109</v>
@@ -4336,10 +4341,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J88" s="7">
         <v>30</v>
@@ -4366,13 +4371,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>161</v>
@@ -4402,10 +4407,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H90" s="8">
+        <v>168</v>
+      </c>
+      <c t="s" r="I90" s="7">
         <v>169</v>
-      </c>
-      <c t="s" r="I90" s="7">
-        <v>170</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>39</v>
@@ -4441,7 +4446,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4453,13 +4458,13 @@
         <v>58</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>158</v>
       </c>
       <c t="s" r="K92" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
@@ -4478,7 +4483,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4490,10 +4495,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I93" s="7">
+        <v>172</v>
+      </c>
+      <c t="s" r="J93" s="7">
         <v>173</v>
-      </c>
-      <c t="s" r="J93" s="7">
-        <v>174</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4526,7 +4531,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4538,15 +4543,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I95" s="7">
+        <v>175</v>
+      </c>
+      <c t="s" r="J95" s="7">
         <v>176</v>
-      </c>
-      <c t="s" r="J95" s="7">
-        <v>177</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4561,7 +4566,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4573,14 +4578,16 @@
         <v>28</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>164</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
-      <c r="M96" s="7"/>
+      <c t="s" r="M96" s="7">
+        <v>179</v>
+      </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c t="s" r="A97" s="6">
@@ -4594,7 +4601,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4627,7 +4634,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4660,7 +4667,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4693,7 +4700,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4726,7 +4733,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4759,7 +4766,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4822,7 +4829,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4953,10 +4960,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5250,7 +5257,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5316,7 +5323,7 @@
         <v>208</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5346,7 +5353,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>209</v>
@@ -5397,7 +5404,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5430,7 +5437,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5930,7 +5937,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>28</v>
@@ -5943,7 +5950,9 @@
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
-      <c r="M141" s="7"/>
+      <c t="s" r="M141" s="7">
+        <v>232</v>
+      </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
       <c t="s" r="A142" s="6">
@@ -5972,7 +5981,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6002,10 +6011,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6035,7 +6044,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>19</v>
@@ -6071,7 +6080,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6091,7 +6100,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6106,7 +6115,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6121,7 +6130,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6139,7 +6148,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6148,13 +6157,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I148" s="7">
         <v>64</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6172,13 +6181,13 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>16</v>
@@ -6205,7 +6214,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6214,10 +6223,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>117</v>
@@ -6238,22 +6247,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6286,7 +6295,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6301,7 +6310,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6319,7 +6328,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6331,10 +6340,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6367,7 +6376,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6385,11 +6394,11 @@
         <v>215</v>
       </c>
       <c t="s" r="K156" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -6404,7 +6413,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6416,10 +6425,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6437,7 +6446,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6449,7 +6458,7 @@
         <v>180</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>45</v>
@@ -6470,7 +6479,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6482,7 +6491,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>116</v>
@@ -6518,7 +6527,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6530,7 +6539,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>51</v>
@@ -6551,7 +6560,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6563,10 +6572,10 @@
         <v>193</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6584,7 +6593,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6593,13 +6602,13 @@
         <v>193</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6617,19 +6626,19 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>193</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>61</v>
@@ -6650,7 +6659,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6662,7 +6671,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>40</v>
@@ -6698,7 +6707,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6713,12 +6722,12 @@
         <v>221</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -6733,7 +6742,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6766,7 +6775,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6778,7 +6787,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>44</v>
@@ -6799,7 +6808,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6814,7 +6823,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6832,7 +6841,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6847,7 +6856,7 @@
         <v>227</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6865,7 +6874,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6877,10 +6886,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6909,23 +6918,23 @@
         <v>7615</v>
       </c>
       <c t="s" r="C174" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>21</v>
@@ -6933,7 +6942,7 @@
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -6944,11 +6953,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C175" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6981,7 +6990,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6993,7 +7002,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>136</v>
@@ -7014,7 +7023,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7047,7 +7056,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7059,7 +7068,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>45</v>
@@ -7095,7 +7104,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7104,10 +7113,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>192</v>
@@ -7128,13 +7137,13 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>16</v>
@@ -7161,7 +7170,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7170,7 +7179,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I182" s="7">
         <v>128</v>
@@ -7194,22 +7203,22 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7242,7 +7251,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7254,7 +7263,7 @@
         <v>193</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>73</v>
@@ -7277,7 +7286,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7292,7 +7301,7 @@
         <v>181</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7310,7 +7319,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7343,7 +7352,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7358,7 +7367,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7376,7 +7385,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7388,10 +7397,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7424,7 +7433,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7436,15 +7445,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -7459,7 +7468,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7471,10 +7480,10 @@
         <v>193</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7492,7 +7501,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7510,7 +7519,7 @@
         <v>198</v>
       </c>
       <c t="s" r="K193" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
@@ -7529,7 +7538,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7541,7 +7550,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>36</v>
@@ -7577,7 +7586,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7586,10 +7595,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>76</v>
@@ -7610,22 +7619,22 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7643,7 +7652,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7652,7 +7661,7 @@
         <v>74</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="I198" s="7">
         <v>57</v>
@@ -7676,19 +7685,19 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>213</v>
@@ -7724,7 +7733,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7757,7 +7766,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7805,7 +7814,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7820,12 +7829,12 @@
         <v>141</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -7840,7 +7849,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7852,10 +7861,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7873,7 +7882,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7885,10 +7894,10 @@
         <v>202</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7906,7 +7915,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7939,7 +7948,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7954,7 +7963,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7972,7 +7981,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7987,7 +7996,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8020,7 +8029,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8032,15 +8041,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8055,7 +8064,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8070,7 +8079,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8088,7 +8097,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8103,7 +8112,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8121,7 +8130,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8133,7 +8142,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>116</v>
@@ -8169,7 +8178,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8181,7 +8190,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>164</v>
@@ -8202,7 +8211,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8235,7 +8244,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8247,10 +8256,10 @@
         <v>180</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8268,7 +8277,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8301,7 +8310,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8310,13 +8319,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8334,19 +8343,19 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>114</v>
@@ -8367,7 +8376,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8379,10 +8388,10 @@
         <v>193</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8400,7 +8409,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8412,7 +8421,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>199</v>
@@ -8448,7 +8457,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8460,10 +8469,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8481,7 +8490,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8493,10 +8502,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8514,7 +8523,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8547,7 +8556,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8595,7 +8604,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8607,7 +8616,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>51</v>
@@ -8615,7 +8624,7 @@
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -8630,7 +8639,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8639,13 +8648,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I231" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8663,22 +8672,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8696,7 +8705,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8708,10 +8717,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8729,7 +8738,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8741,7 +8750,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>146</v>
@@ -8777,7 +8786,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8797,7 +8806,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -8812,7 +8821,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8845,7 +8854,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8857,10 +8866,10 @@
         <v>204</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8878,7 +8887,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8890,10 +8899,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8911,7 +8920,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8923,10 +8932,10 @@
         <v>180</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8944,7 +8953,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8992,7 +9001,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9025,7 +9034,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9037,10 +9046,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9058,7 +9067,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9091,7 +9100,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9103,7 +9112,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>187</v>
@@ -9139,7 +9148,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9151,15 +9160,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9174,7 +9183,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9207,7 +9216,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9219,10 +9228,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9240,7 +9249,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9273,7 +9282,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9288,7 +9297,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9321,13 +9330,13 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>16</v>
@@ -9354,7 +9363,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9387,7 +9396,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9399,10 +9408,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9420,7 +9429,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9429,7 +9438,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>145</v>
@@ -9468,7 +9477,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9483,7 +9492,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9501,7 +9510,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9534,7 +9543,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9543,13 +9552,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9567,13 +9576,13 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>16</v>
@@ -9582,7 +9591,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9615,7 +9624,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9627,15 +9636,15 @@
         <v>193</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -9650,7 +9659,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9665,7 +9674,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9683,7 +9692,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9716,7 +9725,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9728,10 +9737,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9749,7 +9758,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9761,7 +9770,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>158</v>
@@ -9782,7 +9791,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9794,7 +9803,7 @@
         <v>223</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>114</v>
@@ -9815,7 +9824,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9848,7 +9857,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9860,10 +9869,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9896,7 +9905,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9908,15 +9917,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -9931,7 +9940,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -9940,7 +9949,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>164</v>
@@ -9964,22 +9973,22 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9997,7 +10006,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -10012,7 +10021,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10030,7 +10039,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -10042,10 +10051,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10063,7 +10072,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10075,14 +10084,18 @@
         <v>223</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>184</v>
       </c>
-      <c r="K278" s="7"/>
+      <c t="s" r="K278" s="7">
+        <v>88</v>
+      </c>
       <c r="L278" s="7"/>
-      <c r="M278" s="7"/>
+      <c t="s" r="M278" s="7">
+        <v>184</v>
+      </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
       <c t="s" r="A279" s="6">
@@ -10096,7 +10109,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10144,7 +10157,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10177,7 +10190,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10225,7 +10238,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10234,10 +10247,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>18</v>
@@ -10260,13 +10273,13 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>16</v>
@@ -10280,7 +10293,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10295,7 +10308,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10304,7 +10317,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="I286" s="7">
         <v>84</v>
@@ -10328,13 +10341,13 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>16</v>
@@ -10361,7 +10374,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10376,7 +10389,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10394,7 +10407,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10406,7 +10419,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>228</v>
@@ -10427,7 +10440,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10460,7 +10473,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10472,7 +10485,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>145</v>
@@ -10508,7 +10521,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10520,10 +10533,10 @@
         <v>204</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10541,7 +10554,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10553,7 +10566,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>55</v>
@@ -10574,7 +10587,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10586,7 +10599,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>128</v>
@@ -10607,7 +10620,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10619,10 +10632,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10655,7 +10668,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10667,7 +10680,7 @@
         <v>180</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>200</v>
@@ -10675,7 +10688,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -10690,7 +10703,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10702,7 +10715,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>164</v>
@@ -10723,7 +10736,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10735,10 +10748,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10756,7 +10769,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10789,7 +10802,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10804,7 +10817,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10822,7 +10835,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10855,7 +10868,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10867,10 +10880,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10888,7 +10901,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10900,10 +10913,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10921,7 +10934,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -10936,7 +10949,7 @@
         <v>213</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10969,7 +10982,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10981,7 +10994,7 @@
         <v>108</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>190</v>
@@ -10989,7 +11002,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11004,7 +11017,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11016,7 +11029,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>21</v>
@@ -11024,7 +11037,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11039,7 +11052,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11054,7 +11067,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11072,7 +11085,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11084,7 +11097,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>42</v>
@@ -11105,7 +11118,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11114,13 +11127,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11138,22 +11151,22 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11171,7 +11184,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11183,7 +11196,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>80</v>
@@ -11204,7 +11217,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11219,7 +11232,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11237,7 +11250,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11249,10 +11262,10 @@
         <v>207</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11270,7 +11283,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11282,10 +11295,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11318,7 +11331,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11330,7 +11343,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>164</v>
@@ -11351,7 +11364,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11366,7 +11379,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11384,7 +11397,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11393,13 +11406,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11417,22 +11430,22 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11465,7 +11478,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11477,7 +11490,7 @@
         <v>193</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>131</v>
@@ -11485,7 +11498,7 @@
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -11500,7 +11513,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11512,10 +11525,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11533,7 +11546,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11566,7 +11579,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11581,7 +11594,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11599,7 +11612,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11611,7 +11624,7 @@
         <v>189</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>138</v>
@@ -11632,7 +11645,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11647,7 +11660,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11680,7 +11693,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11692,10 +11705,10 @@
         <v>159</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11715,7 +11728,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11748,7 +11761,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11760,10 +11773,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11781,7 +11794,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11814,7 +11827,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11829,7 +11842,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11847,7 +11860,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11859,10 +11872,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11895,7 +11908,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11907,7 +11920,7 @@
         <v>108</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>133</v>
@@ -11928,7 +11941,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11940,7 +11953,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>64</v>
@@ -11961,7 +11974,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11973,7 +11986,7 @@
         <v>159</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>157</v>
@@ -11994,7 +12007,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12006,7 +12019,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>182</v>
@@ -12027,7 +12040,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12039,7 +12052,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>144</v>
@@ -12060,7 +12073,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12075,7 +12088,7 @@
         <v>198</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12093,7 +12106,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12105,10 +12118,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12141,7 +12154,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12153,10 +12166,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12174,7 +12187,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12183,13 +12196,13 @@
         <v>23</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12207,13 +12220,13 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>23</v>
@@ -12222,7 +12235,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12240,7 +12253,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12255,7 +12268,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12273,7 +12286,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12285,7 +12298,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>208</v>
@@ -12306,7 +12319,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12318,10 +12331,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12354,7 +12367,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12387,7 +12400,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12402,7 +12415,7 @@
         <v>155</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12420,7 +12433,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12432,7 +12445,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>78</v>
@@ -12453,7 +12466,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12465,7 +12478,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>205</v>
@@ -12486,7 +12499,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12495,13 +12508,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12519,22 +12532,22 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12567,7 +12580,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12600,7 +12613,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12612,10 +12625,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12633,7 +12646,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12648,7 +12661,7 @@
         <v>181</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12666,7 +12679,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12678,10 +12691,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12699,7 +12712,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12711,10 +12724,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12732,7 +12745,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12741,7 +12754,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>30</v>
@@ -12765,19 +12778,19 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>221</v>
@@ -12813,7 +12826,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12822,17 +12835,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I368" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
-      <c r="M368" s="7"/>
+      <c t="s" r="M368" s="7">
+        <v>379</v>
+      </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
       <c t="s" r="A369" s="6">
@@ -12846,19 +12861,19 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>46</v>
@@ -12879,7 +12894,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12888,10 +12903,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>228</v>
@@ -12912,13 +12927,13 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>74</v>
@@ -12927,7 +12942,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12960,7 +12975,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -12972,10 +12987,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12993,7 +13008,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13008,7 +13023,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13026,7 +13041,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13059,7 +13074,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13071,10 +13086,10 @@
         <v>108</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13092,7 +13107,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13125,7 +13140,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13137,10 +13152,10 @@
         <v>180</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13158,7 +13173,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13170,10 +13185,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13206,7 +13221,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13221,7 +13236,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13239,7 +13254,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13254,7 +13269,7 @@
         <v>154</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13272,7 +13287,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13287,7 +13302,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13305,7 +13320,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13320,7 +13335,7 @@
         <v>227</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13338,7 +13353,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13371,7 +13386,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13383,10 +13398,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13419,7 +13434,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13454,7 +13469,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13487,7 +13502,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13499,7 +13514,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>78</v>
@@ -13520,7 +13535,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13568,7 +13583,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13601,7 +13616,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13634,7 +13649,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13646,10 +13661,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13667,7 +13682,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13700,7 +13715,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13712,7 +13727,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>115</v>
@@ -13733,7 +13748,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13745,7 +13760,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>208</v>
@@ -13766,7 +13781,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -13775,10 +13790,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>22</v>
@@ -13814,7 +13829,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -13829,12 +13844,12 @@
         <v>141</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -13849,7 +13864,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -13861,10 +13876,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13882,7 +13897,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -13894,7 +13909,7 @@
         <v>193</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>215</v>
@@ -13915,7 +13930,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
@@ -13948,7 +13963,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -13960,10 +13975,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13981,7 +13996,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -13993,7 +14008,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>115</v>
@@ -14029,7 +14044,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14041,15 +14056,15 @@
         <v>23</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14064,7 +14079,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14076,7 +14091,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>24</v>
@@ -14097,7 +14112,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14109,10 +14124,10 @@
         <v>180</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14130,7 +14145,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14142,10 +14157,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14163,7 +14178,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14172,10 +14187,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>160</v>
@@ -14196,19 +14211,19 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>187</v>
@@ -14244,7 +14259,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14277,7 +14292,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14289,7 +14304,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>156</v>
@@ -14310,7 +14325,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14322,7 +14337,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>29</v>
@@ -14343,7 +14358,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14376,7 +14391,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14388,10 +14403,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14424,7 +14439,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14444,7 +14459,7 @@
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -14459,7 +14474,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -14471,10 +14486,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14507,7 +14522,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14542,7 +14557,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14575,7 +14590,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -14587,10 +14602,10 @@
         <v>223</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14608,7 +14623,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -14620,7 +14635,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>27</v>
@@ -14641,7 +14656,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -14653,10 +14668,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14674,7 +14689,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -14686,7 +14701,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>57</v>
@@ -14707,7 +14722,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -14740,7 +14755,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
@@ -14755,7 +14770,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14788,22 +14803,22 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14821,7 +14836,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -14830,7 +14845,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I434" s="7">
         <v>67</v>
@@ -14854,13 +14869,13 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>28</v>
@@ -14869,7 +14884,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14887,7 +14902,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -14899,10 +14914,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14935,7 +14950,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -14947,7 +14962,7 @@
         <v>193</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>164</v>
@@ -14968,7 +14983,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -14980,10 +14995,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -15001,7 +15016,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -15013,10 +15028,10 @@
         <v>134</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -15034,7 +15049,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -15046,10 +15061,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15067,7 +15082,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -15079,7 +15094,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J442" s="7">
         <v>39</v>
@@ -15115,7 +15130,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F444" s="7">
         <v>320</v>
@@ -15130,12 +15145,12 @@
         <v>151</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -15150,7 +15165,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
@@ -15183,7 +15198,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
@@ -15216,7 +15231,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
@@ -15231,7 +15246,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15249,7 +15264,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -15264,7 +15279,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15282,7 +15297,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -15315,7 +15330,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -15324,13 +15339,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="I450" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15348,22 +15363,22 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G451" s="8">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="H451" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15396,7 +15411,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F453" s="7">
         <v>330</v>
@@ -15408,15 +15423,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -15431,7 +15446,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -15440,7 +15455,7 @@
         <v>74</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c t="s" r="I454" s="7">
         <v>158</v>
@@ -15464,13 +15479,13 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G455" s="8">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c t="s" r="H455" s="8">
         <v>74</v>
@@ -15512,7 +15527,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F457" s="7">
         <v>330</v>
@@ -15524,10 +15539,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -15545,7 +15560,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -15554,7 +15569,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c t="s" r="I458" s="7">
         <v>64</v>
@@ -15578,13 +15593,13 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c t="s" r="H459" s="8">
         <v>16</v>
@@ -15626,7 +15641,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
@@ -15635,10 +15650,10 @@
         <v>193</v>
       </c>
       <c t="s" r="H461" s="8">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J461" s="7">
         <v>29</v>
@@ -15659,22 +15674,22 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G462" s="8">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c t="s" r="H462" s="8">
         <v>193</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
@@ -15707,22 +15722,22 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -15740,7 +15755,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
@@ -15752,7 +15767,7 @@
         <v>193</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>30</v>
@@ -15773,7 +15788,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
@@ -15782,13 +15797,13 @@
         <v>193</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c t="s" r="I466" s="7">
         <v>138</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
@@ -15817,11 +15832,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C468" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F468" s="7">
         <v>330</v>
@@ -15830,13 +15845,13 @@
         <v>193</v>
       </c>
       <c t="s" r="H468" s="8">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
@@ -15850,17 +15865,17 @@
         <v>5806</v>
       </c>
       <c t="s" r="C469" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G469" s="8">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c t="s" r="H469" s="8">
         <v>193</v>
@@ -15869,7 +15884,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
@@ -15902,7 +15917,7 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
@@ -15911,10 +15926,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H471" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J471" s="7">
         <v>187</v>
@@ -15935,19 +15950,19 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F472" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G472" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="H472" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c t="s" r="J472" s="7">
         <v>221</v>
@@ -15958,7 +15973,7 @@
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c t="s" r="A473" s="9">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B473" s="9"/>
       <c r="C473" s="9"/>
@@ -15978,7 +15993,7 @@
     <row r="474" ht="65.25" customHeight="1"/>
     <row r="475" ht="17.25" customHeight="1">
       <c t="s" r="A475" s="10">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B475" s="10"/>
       <c r="C475" s="10"/>
@@ -15991,7 +16006,7 @@
       <c r="J475" s="10"/>
       <c r="K475" s="10"/>
       <c t="s" r="L475" s="11">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M475" s="11"/>
       <c r="N475" s="11"/>

--- a/Data/FlightPlan/FPL_17AUG26.xlsx
+++ b/Data/FlightPlan/FPL_17AUG26.xlsx
@@ -341,6 +341,9 @@
     <t>16:30</t>
   </si>
   <si>
+    <t>16:23</t>
+  </si>
+  <si>
     <t>17:05</t>
   </si>
   <si>
@@ -590,216 +593,216 @@
     <t>VN-A536</t>
   </si>
   <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>07:02</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>10:38</t>
+  </si>
+  <si>
+    <t>12:37</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:22</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>14:54</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>14:57</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>16:51</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>13:44</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>17:19</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>VN-A550</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:42</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
     <t>16:00</t>
   </si>
   <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>07:02</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>10:38</t>
-  </si>
-  <si>
-    <t>12:37</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:22</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:53</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>14:54</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>14:57</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>16:51</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>13:44</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>17:19</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>VN-A550</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:42</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>12:56</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
     <t>19:05</t>
   </si>
   <si>
@@ -989,6 +992,12 @@
     <t>14:26</t>
   </si>
   <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
     <t>VN-A632</t>
   </si>
   <si>
@@ -1019,6 +1028,12 @@
     <t>13:20</t>
   </si>
   <si>
+    <t>16:54</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
     <t>VN-A634</t>
   </si>
   <si>
@@ -1073,10 +1088,7 @@
     <t>TBB</t>
   </si>
   <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>22:15</t>
+    <t>17:07</t>
   </si>
   <si>
     <t>VN-A639</t>
@@ -1322,6 +1334,9 @@
     <t>14:34</t>
   </si>
   <si>
+    <t>16:32</t>
+  </si>
+  <si>
     <t>VN-A662</t>
   </si>
   <si>
@@ -1337,9 +1352,6 @@
     <t>12:58</t>
   </si>
   <si>
-    <t>15:57</t>
-  </si>
-  <si>
     <t>21:50</t>
   </si>
   <si>
@@ -1349,9 +1361,6 @@
     <t>13:41</t>
   </si>
   <si>
-    <t>16:32</t>
-  </si>
-  <si>
     <t>01:15</t>
   </si>
   <si>
@@ -1397,6 +1406,9 @@
     <t>13:19</t>
   </si>
   <si>
+    <t>16:47</t>
+  </si>
+  <si>
     <t>03:55</t>
   </si>
   <si>
@@ -1586,7 +1598,7 @@
     <t>MEL</t>
   </si>
   <si>
-    <t>23:01</t>
+    <t>22:58</t>
   </si>
   <si>
     <t>VN-A814</t>
@@ -1619,7 +1631,7 @@
     <t>KZN</t>
   </si>
   <si>
-    <t>14:03</t>
+    <t>14:01</t>
   </si>
   <si>
     <t>VN-A820</t>
@@ -1637,7 +1649,7 @@
     <t>Total Record(s): 389</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 17, 2026 15:06</t>
+    <t xml:space="preserve">Generated on  Aug 17, 2026 15:24</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3310,7 +3322,9 @@
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
+      <c t="s" r="M42" s="7">
+        <v>110</v>
+      </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c t="s" r="A43" s="6">
@@ -3336,10 +3350,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -3366,13 +3380,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -3396,16 +3410,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H45" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3438,27 +3452,27 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3473,7 +3487,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3482,18 +3496,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c t="s" r="M48" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -3508,13 +3522,13 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>16</v>
@@ -3523,7 +3537,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3541,7 +3555,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3550,13 +3564,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="I50" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3574,22 +3588,22 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="H51" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3607,7 +3621,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3619,10 +3633,10 @@
         <v>97</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3655,7 +3669,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3670,14 +3684,14 @@
         <v>58</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="K54" s="7">
         <v>25</v>
       </c>
       <c r="L54" s="7"/>
       <c t="s" r="M54" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
@@ -3692,7 +3706,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3701,7 +3715,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I55" s="7">
         <v>91</v>
@@ -3712,7 +3726,7 @@
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
       <c t="s" r="M55" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -3727,13 +3741,13 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>31</v>
@@ -3742,7 +3756,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3760,7 +3774,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3808,7 +3822,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3817,13 +3831,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I59" s="7">
         <v>42</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3843,13 +3857,13 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>31</v>
@@ -3863,7 +3877,7 @@
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3878,7 +3892,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3887,7 +3901,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I61" s="7">
         <v>53</v>
@@ -3926,7 +3940,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3938,15 +3952,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c t="s" r="M63" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -3961,7 +3975,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3973,15 +3987,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -3996,7 +4010,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -4005,10 +4019,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>29</v>
@@ -4018,7 +4032,7 @@
       </c>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -4033,19 +4047,19 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G66" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H66" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J66" s="7">
         <v>92</v>
@@ -4053,7 +4067,7 @@
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -4068,7 +4082,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4077,13 +4091,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -4101,22 +4115,22 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -4149,7 +4163,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4169,7 +4183,7 @@
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -4184,7 +4198,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4193,13 +4207,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -4217,22 +4231,22 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H72" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -4265,7 +4279,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4280,12 +4294,12 @@
         <v>86</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4300,7 +4314,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4320,7 +4334,7 @@
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4350,7 +4364,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4362,7 +4376,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J77" s="7">
         <v>71</v>
@@ -4370,7 +4384,7 @@
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4385,7 +4399,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4397,15 +4411,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4420,7 +4434,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4432,15 +4446,15 @@
         <v>41</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4455,7 +4469,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4467,17 +4481,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="K80" s="7">
         <v>73</v>
       </c>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4492,7 +4506,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4501,20 +4515,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="K81" s="7">
         <v>80</v>
       </c>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4529,29 +4543,29 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="H82" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="K82" s="7">
         <v>49</v>
       </c>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4581,7 +4595,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4590,13 +4604,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4616,13 +4630,13 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>16</v>
@@ -4634,11 +4648,11 @@
         <v>106</v>
       </c>
       <c t="s" r="K85" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4653,7 +4667,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4662,18 +4676,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4688,13 +4702,13 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>16</v>
@@ -4703,7 +4717,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4721,7 +4735,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4733,10 +4747,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4769,7 +4783,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4784,14 +4798,14 @@
         <v>100</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="K90" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4806,7 +4820,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4818,10 +4832,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4854,7 +4868,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4866,15 +4880,15 @@
         <v>75</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -4889,7 +4903,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4901,15 +4915,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -4924,7 +4938,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4933,18 +4947,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I95" s="7">
         <v>98</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4959,13 +4973,13 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>31</v>
@@ -4979,7 +4993,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4994,7 +5008,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -5006,15 +5020,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5029,7 +5043,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5041,7 +5055,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>82</v>
@@ -5062,7 +5076,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5077,7 +5091,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5095,7 +5109,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5110,7 +5124,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -5143,7 +5157,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5152,18 +5166,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5178,13 +5192,13 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>31</v>
@@ -5193,7 +5207,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -5213,7 +5227,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5225,7 +5239,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>35</v>
@@ -5246,7 +5260,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5258,10 +5272,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5294,7 +5308,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5306,15 +5320,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5329,7 +5343,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5344,7 +5358,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5362,7 +5376,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5374,7 +5388,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>65</v>
@@ -5395,7 +5409,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5407,10 +5421,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5443,7 +5457,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5452,13 +5466,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5478,27 +5492,27 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5513,7 +5527,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5522,13 +5536,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="I114" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5546,22 +5560,22 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5579,7 +5593,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5588,10 +5602,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>42</v>
@@ -5627,7 +5641,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5636,13 +5650,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I118" s="7">
         <v>42</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5662,13 +5676,13 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>16</v>
@@ -5677,12 +5691,12 @@
         <v>61</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5697,7 +5711,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5709,10 +5723,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5745,7 +5759,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5754,10 +5768,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>107</v>
@@ -5765,7 +5779,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -5780,13 +5794,13 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>16</v>
@@ -5795,12 +5809,12 @@
         <v>73</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5815,7 +5829,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5824,13 +5838,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="I124" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5848,22 +5862,22 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5896,7 +5910,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5908,15 +5922,15 @@
         <v>41</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -5931,7 +5945,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5940,18 +5954,18 @@
         <v>41</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5966,27 +5980,27 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6001,7 +6015,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6021,7 +6035,7 @@
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6036,7 +6050,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6045,18 +6059,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>253</v>
+        <v>194</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6071,13 +6085,13 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>16</v>
@@ -6104,7 +6118,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6119,7 +6133,7 @@
         <v>256</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -6137,7 +6151,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6191,7 +6205,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>31</v>
@@ -6240,7 +6254,7 @@
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>193</v>
+        <v>263</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6270,7 +6284,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6300,7 +6314,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>19</v>
@@ -6336,7 +6350,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6345,10 +6359,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>86</v>
@@ -6356,7 +6370,7 @@
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6371,13 +6385,13 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>16</v>
@@ -6386,12 +6400,12 @@
         <v>58</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6406,7 +6420,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6415,18 +6429,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6441,19 +6455,19 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>109</v>
@@ -6461,7 +6475,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6476,7 +6490,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6485,10 +6499,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>258</v>
@@ -6509,22 +6523,22 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6557,7 +6571,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6569,10 +6583,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6590,7 +6604,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6602,10 +6616,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6638,7 +6652,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6647,20 +6661,20 @@
         <v>66</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>107</v>
       </c>
       <c t="s" r="K151" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6675,13 +6689,13 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>16</v>
@@ -6690,7 +6704,7 @@
         <v>262</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6708,7 +6722,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6717,7 +6731,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I153" s="7">
         <v>92</v>
@@ -6741,22 +6755,22 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6789,7 +6803,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6801,7 +6815,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>55</v>
@@ -6809,7 +6823,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -6824,7 +6838,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6833,18 +6847,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6859,19 +6873,19 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>94</v>
@@ -6879,7 +6893,7 @@
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6894,19 +6908,19 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>67</v>
@@ -6927,19 +6941,19 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>66</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>43</v>
@@ -6975,7 +6989,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6987,15 +7001,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -7010,7 +7024,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -7025,12 +7039,12 @@
         <v>43</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7045,7 +7059,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7065,7 +7079,7 @@
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7080,7 +7094,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7100,7 +7114,7 @@
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7115,7 +7129,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7127,10 +7141,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -7148,7 +7162,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7160,10 +7174,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7192,23 +7206,23 @@
         <v>7615</v>
       </c>
       <c t="s" r="C169" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>21</v>
@@ -7216,7 +7230,7 @@
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7227,11 +7241,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C170" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7240,18 +7254,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7266,27 +7280,27 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7301,7 +7315,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7310,13 +7324,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7334,19 +7348,19 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>49</v>
@@ -7367,7 +7381,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7379,7 +7393,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>39</v>
@@ -7415,7 +7429,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7424,18 +7438,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7450,27 +7464,27 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7485,7 +7499,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7494,13 +7508,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>109</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7518,22 +7532,22 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7566,7 +7580,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7575,10 +7589,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>88</v>
@@ -7601,27 +7615,27 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7636,7 +7650,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7645,13 +7659,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>254</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7669,22 +7683,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7702,7 +7716,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7714,10 +7728,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7750,7 +7764,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7762,15 +7776,15 @@
         <v>24</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7785,7 +7799,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7794,18 +7808,18 @@
         <v>24</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7820,26 +7834,30 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>113</v>
-      </c>
-      <c r="K189" s="7"/>
+        <v>114</v>
+      </c>
+      <c t="s" r="K189" s="7">
+        <v>327</v>
+      </c>
       <c r="L189" s="7"/>
-      <c r="M189" s="7"/>
+      <c t="s" r="M189" s="7">
+        <v>328</v>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c r="A190" s="6"/>
@@ -7868,7 +7886,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7877,18 +7895,18 @@
         <v>75</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -7903,27 +7921,27 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>75</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -7938,7 +7956,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7947,13 +7965,13 @@
         <v>75</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>62</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7971,22 +7989,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>75</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -8019,7 +8037,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8039,7 +8057,7 @@
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8054,7 +8072,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8063,20 +8081,20 @@
         <v>31</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="K197" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>109</v>
+        <v>339</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8091,29 +8109,29 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>81</v>
       </c>
       <c t="s" r="K198" s="7">
-        <v>110</v>
+        <v>340</v>
       </c>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8128,7 +8146,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8137,7 +8155,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>62</v>
@@ -8145,9 +8163,13 @@
       <c t="s" r="J199" s="7">
         <v>35</v>
       </c>
-      <c r="K199" s="7"/>
+      <c t="s" r="K199" s="7">
+        <v>130</v>
+      </c>
       <c r="L199" s="7"/>
-      <c r="M199" s="7"/>
+      <c t="s" r="M199" s="7">
+        <v>184</v>
+      </c>
     </row>
     <row r="200" ht="15" customHeight="1">
       <c r="A200" s="6"/>
@@ -8176,7 +8198,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8185,18 +8207,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8211,13 +8233,13 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>16</v>
@@ -8226,12 +8248,12 @@
         <v>104</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8246,7 +8268,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8255,10 +8277,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>91</v>
@@ -8266,7 +8288,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8281,13 +8303,13 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>16</v>
@@ -8296,12 +8318,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8316,7 +8338,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8325,7 +8347,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c t="s" r="I205" s="7">
         <v>77</v>
@@ -8349,22 +8371,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8382,7 +8404,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8394,10 +8416,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8430,7 +8452,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8442,15 +8464,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8465,7 +8487,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8477,7 +8499,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>106</v>
@@ -8485,7 +8507,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8500,7 +8522,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8512,7 +8534,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>92</v>
@@ -8533,7 +8555,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8545,10 +8567,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8581,7 +8603,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8593,15 +8615,15 @@
         <v>75</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8616,7 +8638,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8631,12 +8653,12 @@
         <v>98</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8651,7 +8673,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8660,10 +8682,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>89</v>
@@ -8671,7 +8693,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8686,19 +8708,19 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>29</v>
@@ -8706,7 +8728,7 @@
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8721,7 +8743,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8730,7 +8752,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c t="s" r="I218" s="7">
         <v>108</v>
@@ -8740,7 +8762,9 @@
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
-      <c r="M218" s="7"/>
+      <c t="s" r="M218" s="7">
+        <v>359</v>
+      </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
       <c t="s" r="A219" s="6">
@@ -8754,22 +8778,22 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8787,7 +8811,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8796,13 +8820,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8820,22 +8844,22 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>355</v>
+        <v>327</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8868,7 +8892,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8880,15 +8904,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8903,7 +8927,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8915,15 +8939,15 @@
         <v>75</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8938,7 +8962,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8950,17 +8974,17 @@
         <v>31</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>61</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8975,7 +8999,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9027,7 +9051,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9039,7 +9063,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>55</v>
@@ -9062,7 +9086,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9071,7 +9095,7 @@
         <v>75</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I229" s="7">
         <v>50</v>
@@ -9082,7 +9106,7 @@
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9097,19 +9121,19 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>94</v>
@@ -9130,7 +9154,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9142,10 +9166,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -9163,7 +9187,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9175,10 +9199,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -9211,7 +9235,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9220,7 +9244,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I234" s="7">
         <v>45</v>
@@ -9231,7 +9255,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9246,13 +9270,13 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>31</v>
@@ -9266,7 +9290,7 @@
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9281,7 +9305,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9290,13 +9314,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I236" s="7">
         <v>32</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -9314,13 +9338,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>31</v>
@@ -9347,7 +9371,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9359,7 +9383,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>257</v>
@@ -9380,7 +9404,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9392,7 +9416,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>258</v>
@@ -9428,7 +9452,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9440,7 +9464,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>39</v>
@@ -9448,7 +9472,7 @@
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9463,7 +9487,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9483,7 +9507,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9498,7 +9522,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9507,10 +9531,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>89</v>
@@ -9533,27 +9557,27 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9568,7 +9592,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9577,13 +9601,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9601,13 +9625,13 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>16</v>
@@ -9616,7 +9640,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9649,7 +9673,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9658,18 +9682,18 @@
         <v>75</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9684,22 +9708,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9717,7 +9741,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9726,13 +9750,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I250" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9750,22 +9774,22 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>75</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9798,7 +9822,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9810,15 +9834,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9833,7 +9857,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9845,7 +9869,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>27</v>
@@ -9868,7 +9892,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9880,15 +9904,15 @@
         <v>75</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9903,7 +9927,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9912,7 +9936,7 @@
         <v>75</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I256" s="7">
         <v>109</v>
@@ -9936,22 +9960,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9984,19 +10008,19 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>254</v>
@@ -10004,7 +10028,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10019,7 +10043,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10028,13 +10052,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -10052,19 +10076,19 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>95</v>
@@ -10085,7 +10109,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10094,10 +10118,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>42</v>
@@ -10133,7 +10157,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10142,18 +10166,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10168,13 +10192,13 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>16</v>
@@ -10183,12 +10207,12 @@
         <v>107</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10203,7 +10227,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10212,13 +10236,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>108</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -10236,22 +10260,22 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -10284,7 +10308,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10293,18 +10317,18 @@
         <v>75</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10319,13 +10343,13 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>75</v>
@@ -10334,12 +10358,12 @@
         <v>42</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10354,7 +10378,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10369,12 +10393,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10389,7 +10413,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10404,12 +10428,12 @@
         <v>106</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10424,7 +10448,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10436,15 +10460,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10459,7 +10483,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10468,13 +10492,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10492,22 +10516,22 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10525,7 +10549,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10537,10 +10561,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10573,7 +10597,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10585,15 +10609,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10608,7 +10632,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10617,18 +10641,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10643,27 +10667,27 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10678,7 +10702,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10690,15 +10714,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10713,7 +10737,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10728,7 +10752,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10746,7 +10770,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10755,10 +10779,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>82</v>
@@ -10783,13 +10807,13 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>16</v>
@@ -10798,7 +10822,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10831,7 +10855,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10851,7 +10875,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10866,7 +10890,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10878,7 +10902,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>73</v>
@@ -10886,7 +10910,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10901,7 +10925,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10910,13 +10934,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10934,22 +10958,22 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10982,7 +11006,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10991,10 +11015,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>18</v>
@@ -11017,13 +11041,13 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>16</v>
@@ -11032,12 +11056,12 @@
         <v>39</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11052,7 +11076,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -11061,18 +11085,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>98</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11087,13 +11111,13 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>16</v>
@@ -11107,7 +11131,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11122,7 +11146,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -11137,12 +11161,12 @@
         <v>61</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11157,7 +11181,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11169,7 +11193,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>255</v>
@@ -11190,7 +11214,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -11202,7 +11226,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>83</v>
@@ -11223,7 +11247,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11238,7 +11262,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -11271,7 +11295,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11280,18 +11304,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11306,19 +11330,19 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>59</v>
@@ -11341,7 +11365,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11353,10 +11377,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11376,7 +11400,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -11388,7 +11412,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>94</v>
@@ -11424,7 +11448,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11433,18 +11457,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11459,27 +11483,27 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11494,7 +11518,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11506,15 +11530,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11529,7 +11553,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11547,11 +11571,11 @@
         <v>46</v>
       </c>
       <c t="s" r="K308" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11566,7 +11590,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11578,17 +11602,17 @@
         <v>31</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="K309" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11603,7 +11627,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11612,10 +11636,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>33</v>
@@ -11636,22 +11660,22 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11684,7 +11708,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11693,18 +11717,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11719,19 +11743,19 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>21</v>
@@ -11739,7 +11763,7 @@
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11754,7 +11778,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11763,18 +11787,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11789,19 +11813,19 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>46</v>
@@ -11809,7 +11833,7 @@
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11824,7 +11848,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11833,18 +11857,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11859,19 +11883,19 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>262</v>
@@ -11892,7 +11916,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11904,10 +11928,10 @@
         <v>64</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11925,7 +11949,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11940,7 +11964,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11958,7 +11982,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11967,13 +11991,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11991,22 +12015,22 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -12039,7 +12063,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -12051,15 +12075,15 @@
         <v>75</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12074,7 +12098,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -12086,10 +12110,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -12109,7 +12133,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -12124,12 +12148,12 @@
         <v>59</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12144,7 +12168,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -12156,14 +12180,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>254</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
-      <c r="M327" s="7"/>
+      <c t="s" r="M327" s="7">
+        <v>441</v>
+      </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
       <c t="s" r="A328" s="6">
@@ -12177,7 +12203,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12189,10 +12215,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -12210,7 +12236,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12222,10 +12248,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -12258,7 +12284,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12267,18 +12293,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12293,27 +12319,27 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12328,7 +12354,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12337,7 +12363,7 @@
         <v>31</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>70</v>
@@ -12348,7 +12374,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12363,13 +12389,13 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>31</v>
@@ -12378,12 +12404,12 @@
         <v>61</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>442</v>
+        <v>254</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12398,7 +12424,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12407,13 +12433,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I335" s="7">
         <v>79</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12431,22 +12457,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12479,7 +12505,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12488,18 +12514,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12514,13 +12540,13 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>16</v>
@@ -12529,12 +12555,12 @@
         <v>86</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12549,7 +12575,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12569,7 +12595,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12584,7 +12610,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12593,18 +12619,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12619,13 +12645,13 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>31</v>
@@ -12634,7 +12660,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12652,7 +12678,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12661,13 +12687,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12685,22 +12711,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12733,7 +12759,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12742,13 +12768,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12768,19 +12794,19 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>70</v>
@@ -12788,7 +12814,7 @@
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12803,7 +12829,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12812,18 +12838,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12838,27 +12864,27 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12873,7 +12899,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12882,13 +12908,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12906,22 +12932,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12954,7 +12980,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12966,15 +12992,15 @@
         <v>24</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12989,7 +13015,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12998,18 +13024,18 @@
         <v>24</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13024,27 +13050,27 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13059,7 +13085,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -13071,10 +13097,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -13092,7 +13118,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13104,10 +13130,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13125,7 +13151,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -13137,10 +13163,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13173,7 +13199,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -13185,15 +13211,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13208,7 +13234,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -13220,7 +13246,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>91</v>
@@ -13228,7 +13254,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13243,7 +13269,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -13258,11 +13284,13 @@
         <v>76</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
-      <c r="M362" s="7"/>
+      <c t="s" r="M362" s="7">
+        <v>465</v>
+      </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
       <c t="s" r="A363" s="6">
@@ -13276,7 +13304,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -13288,10 +13316,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -13309,7 +13337,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -13318,13 +13346,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -13342,22 +13370,22 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13390,7 +13418,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13405,12 +13433,12 @@
         <v>39</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13425,7 +13453,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13437,15 +13465,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13460,7 +13488,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13472,15 +13500,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13495,7 +13523,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13507,17 +13535,17 @@
         <v>31</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="K370" s="7">
         <v>28</v>
       </c>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13532,7 +13560,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13544,17 +13572,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>80</v>
       </c>
       <c t="s" r="K371" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13569,7 +13597,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13581,17 +13609,17 @@
         <v>31</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="K372" s="7">
         <v>92</v>
       </c>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13621,7 +13649,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13630,18 +13658,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -13656,19 +13684,19 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>75</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>50</v>
@@ -13691,7 +13719,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13700,10 +13728,10 @@
         <v>75</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>255</v>
@@ -13711,7 +13739,7 @@
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13726,22 +13754,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>75</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13759,7 +13787,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13771,10 +13799,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13807,7 +13835,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13819,15 +13847,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -13842,7 +13870,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13857,12 +13885,12 @@
         <v>55</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13877,7 +13905,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13899,7 +13927,7 @@
       </c>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -13914,7 +13942,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13923,13 +13951,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13947,13 +13975,13 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>16</v>
@@ -13962,7 +13990,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13980,7 +14008,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13989,10 +14017,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>95</v>
@@ -14013,22 +14041,22 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -14061,7 +14089,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -14076,12 +14104,12 @@
         <v>88</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14096,7 +14124,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14108,15 +14136,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14131,7 +14159,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -14151,7 +14179,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14166,7 +14194,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14178,10 +14206,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -14199,7 +14227,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14211,10 +14239,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -14232,7 +14260,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14244,10 +14272,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -14280,7 +14308,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14292,7 +14320,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>86</v>
@@ -14315,7 +14343,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14327,7 +14355,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>28</v>
@@ -14335,7 +14363,7 @@
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14350,7 +14378,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14365,12 +14393,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14385,7 +14413,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14433,7 +14461,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -14448,12 +14476,12 @@
         <v>39</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14468,7 +14496,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -14480,10 +14508,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14503,7 +14531,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -14515,15 +14543,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14538,7 +14566,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -14553,12 +14581,12 @@
         <v>73</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14573,7 +14601,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
@@ -14585,10 +14613,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -14606,7 +14634,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -14618,10 +14646,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14639,7 +14667,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -14648,10 +14676,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>22</v>
@@ -14687,7 +14715,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -14699,15 +14727,15 @@
         <v>64</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14722,7 +14750,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -14734,15 +14762,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14757,7 +14785,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -14766,18 +14794,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14792,22 +14820,22 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14825,7 +14853,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -14837,10 +14865,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14858,7 +14886,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14870,7 +14898,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>83</v>
@@ -14906,7 +14934,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14918,15 +14946,15 @@
         <v>24</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -14941,7 +14969,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14961,7 +14989,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14976,7 +15004,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14985,20 +15013,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="K417" s="7">
         <v>70</v>
       </c>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -15013,29 +15041,29 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c t="s" r="K418" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15050,7 +15078,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15062,7 +15090,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>93</v>
@@ -15083,7 +15111,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15098,7 +15126,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -15131,7 +15159,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15140,7 +15168,7 @@
         <v>75</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="I422" s="7">
         <v>55</v>
@@ -15166,27 +15194,27 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>75</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15201,7 +15229,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -15213,7 +15241,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>32</v>
@@ -15221,7 +15249,7 @@
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -15236,7 +15264,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -15269,7 +15297,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15281,10 +15309,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -15317,7 +15345,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -15326,18 +15354,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15352,22 +15380,22 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -15400,7 +15428,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
@@ -15409,10 +15437,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>69</v>
@@ -15435,13 +15463,13 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>31</v>
@@ -15455,7 +15483,7 @@
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15470,7 +15498,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -15479,13 +15507,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -15505,13 +15533,13 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>31</v>
@@ -15525,7 +15553,7 @@
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -15540,7 +15568,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -15549,13 +15577,13 @@
         <v>31</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -15573,29 +15601,29 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H436" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="K436" s="7">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15625,7 +15653,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -15637,15 +15665,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -15660,7 +15688,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -15669,18 +15697,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="I439" s="7">
         <v>73</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15695,22 +15723,22 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="H440" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -15728,7 +15756,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -15740,10 +15768,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15776,7 +15804,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -15785,18 +15813,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15811,27 +15839,27 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -15861,7 +15889,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
@@ -15870,18 +15898,18 @@
         <v>31</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15896,13 +15924,13 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>31</v>
@@ -15916,7 +15944,7 @@
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -15931,7 +15959,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -15940,10 +15968,10 @@
         <v>31</v>
       </c>
       <c t="s" r="H448" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>107</v>
@@ -15951,7 +15979,7 @@
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -15966,19 +15994,19 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G449" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H449" s="8">
         <v>31</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>32</v>
@@ -15986,7 +16014,7 @@
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -16001,7 +16029,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -16013,10 +16041,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -16034,7 +16062,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -16049,7 +16077,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -16067,7 +16095,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -16079,10 +16107,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -16115,7 +16143,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -16127,15 +16155,15 @@
         <v>75</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -16150,7 +16178,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
@@ -16159,13 +16187,13 @@
         <v>75</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -16183,13 +16211,13 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c t="s" r="H456" s="8">
         <v>75</v>
@@ -16231,27 +16259,27 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G458" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H458" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c t="s" r="M458" s="7">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="459" ht="14.25" customHeight="1">
@@ -16266,7 +16294,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
@@ -16275,18 +16303,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c t="s" r="I459" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -16301,13 +16329,13 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c t="s" r="H460" s="8">
         <v>16</v>
@@ -16316,7 +16344,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -16349,16 +16377,16 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G462" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H462" s="8">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c t="s" r="I462" s="7">
         <v>104</v>
@@ -16384,22 +16412,22 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G463" s="8">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -16432,19 +16460,19 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G465" s="8">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c t="s" r="H465" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>262</v>
@@ -16452,7 +16480,7 @@
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -16467,7 +16495,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
@@ -16476,20 +16504,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J466" s="7">
         <v>33</v>
       </c>
       <c t="s" r="K466" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L466" s="7"/>
       <c t="s" r="M466" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="467" ht="14.25" customHeight="1">
@@ -16504,29 +16532,29 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="K467" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L467" s="7"/>
       <c t="s" r="M467" s="7">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
@@ -16552,31 +16580,31 @@
         <v>5805</v>
       </c>
       <c t="s" r="C469" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G469" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="H469" s="8">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -16587,26 +16615,26 @@
         <v>5806</v>
       </c>
       <c t="s" r="C470" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G470" s="8">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -16639,7 +16667,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="F472" s="7">
         <v>330</v>
@@ -16648,18 +16676,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H472" s="8">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
       <c t="s" r="M472" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="473" ht="14.25" customHeight="1">
@@ -16674,22 +16702,22 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="F473" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G473" s="8">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c t="s" r="H473" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -16697,7 +16725,7 @@
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c t="s" r="A474" s="9">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B474" s="9"/>
       <c r="C474" s="9"/>
@@ -16717,7 +16745,7 @@
     <row r="475" ht="66" customHeight="1"/>
     <row r="476" ht="16.5" customHeight="1">
       <c t="s" r="A476" s="10">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B476" s="10"/>
       <c r="C476" s="10"/>
@@ -16730,7 +16758,7 @@
       <c r="J476" s="10"/>
       <c r="K476" s="10"/>
       <c t="s" r="L476" s="11">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="M476" s="11"/>
       <c r="N476" s="11"/>
